--- a/総合課題.xlsx
+++ b/総合課題.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Isserv-dc4\研修用\教材\研修用問題\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\kenshu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBA9D860-8341-4367-831D-3E7ED6B66E69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE0EADB7-45D4-4599-8AA2-27D9F0D14C0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="メモ" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="229">
   <si>
     <t>Java</t>
     <phoneticPr fontId="1"/>
@@ -3487,6 +3487,10 @@
     <rPh sb="175" eb="176">
       <t>オモ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>あ</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4146,7 +4150,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="B3:D15"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="3" spans="2:4">
       <c r="B3" t="s">
@@ -4211,21 +4215,26 @@
   <sheetPr codeName="Sheet2">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:L35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25"/>
+  <dimension ref="A1:L35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="10.8"/>
   <cols>
     <col min="1" max="1" width="1.5" style="2" customWidth="1"/>
-    <col min="2" max="2" width="4.125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="5.625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="19.75" style="2" customWidth="1"/>
-    <col min="5" max="5" width="69.625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="32.25" style="2" customWidth="1"/>
-    <col min="7" max="7" width="22.125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="17.375" style="2" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="4.09765625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="5.59765625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="19.69921875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="69.59765625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="32.19921875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="22.09765625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="17.3984375" style="2" hidden="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9">
+    <row r="1" spans="1:9">
+      <c r="A1" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="B2" s="2" t="s">
         <v>23</v>
       </c>
@@ -4233,7 +4242,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="2:9">
+    <row r="3" spans="1:9">
       <c r="B3" s="2" t="s">
         <v>83</v>
       </c>
@@ -4245,12 +4254,12 @@
         <v>470分</v>
       </c>
     </row>
-    <row r="4" spans="2:9">
+    <row r="4" spans="1:9">
       <c r="B4" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="2:9">
+    <row r="5" spans="1:9">
       <c r="B5" s="1" t="s">
         <v>10</v>
       </c>
@@ -4273,7 +4282,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="31.5" customHeight="1">
+    <row r="6" spans="1:9" ht="31.5" customHeight="1">
       <c r="B6" s="45">
         <v>1</v>
       </c>
@@ -4296,7 +4305,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="31.5" customHeight="1">
+    <row r="7" spans="1:9" ht="31.5" customHeight="1">
       <c r="B7" s="46"/>
       <c r="C7" s="49"/>
       <c r="D7" s="4" t="s">
@@ -4311,7 +4320,7 @@
       <c r="G7" s="5"/>
       <c r="H7" s="6"/>
     </row>
-    <row r="8" spans="2:9" ht="31.5" customHeight="1">
+    <row r="8" spans="1:9" ht="31.5" customHeight="1">
       <c r="B8" s="47"/>
       <c r="C8" s="50"/>
       <c r="D8" s="4" t="s">
@@ -4328,7 +4337,7 @@
       </c>
       <c r="H8" s="6"/>
     </row>
-    <row r="9" spans="2:9" ht="29.25" customHeight="1">
+    <row r="9" spans="1:9" ht="29.25" customHeight="1">
       <c r="B9" s="3">
         <v>2</v>
       </c>
@@ -4351,7 +4360,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:9" ht="75" customHeight="1">
+    <row r="10" spans="1:9" ht="75" customHeight="1">
       <c r="B10" s="3">
         <v>3</v>
       </c>
@@ -4374,7 +4383,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="2:9" ht="48.75" customHeight="1">
+    <row r="11" spans="1:9" ht="48.75" customHeight="1">
       <c r="B11" s="3">
         <v>4</v>
       </c>
@@ -4393,18 +4402,18 @@
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
     </row>
-    <row r="12" spans="2:9">
+    <row r="12" spans="1:9">
       <c r="H12" s="10">
         <f>SUM(H6:H11)</f>
         <v>70</v>
       </c>
     </row>
-    <row r="13" spans="2:9">
+    <row r="13" spans="1:9">
       <c r="B13" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="2:9">
+    <row r="14" spans="1:9">
       <c r="B14" s="1" t="s">
         <v>10</v>
       </c>
@@ -4427,7 +4436,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="15" spans="2:9" ht="33.75">
+    <row r="15" spans="1:9" ht="32.4">
       <c r="B15" s="3">
         <v>1</v>
       </c>
@@ -4446,7 +4455,7 @@
       </c>
       <c r="H15" s="6"/>
     </row>
-    <row r="16" spans="2:9" ht="66" customHeight="1">
+    <row r="16" spans="1:9" ht="66" customHeight="1">
       <c r="B16" s="3">
         <f>B15+1</f>
         <v>2</v>
@@ -4928,12 +4937,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{724A5114-3F2C-4D91-AFFC-A3EE2AC05F83}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="B4:I92"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="23.5" customWidth="1"/>
-    <col min="3" max="3" width="19.375" customWidth="1"/>
+    <col min="3" max="3" width="19.3984375" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="7" max="7" width="19.25" customWidth="1"/>
+    <col min="7" max="7" width="19.19921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="4" spans="2:9" ht="36">
@@ -5089,7 +5098,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="17" spans="2:6" ht="19.5" thickBot="1">
+    <row r="17" spans="2:6" ht="18.600000000000001" thickBot="1">
       <c r="B17" s="28">
         <v>37651</v>
       </c>
@@ -5106,7 +5115,7 @@
         <v>45294</v>
       </c>
     </row>
-    <row r="18" spans="2:6" ht="19.5" thickBot="1">
+    <row r="18" spans="2:6" ht="18.600000000000001" thickBot="1">
       <c r="B18" s="28">
         <v>100807</v>
       </c>
@@ -5123,7 +5132,7 @@
         <v>44895</v>
       </c>
     </row>
-    <row r="19" spans="2:6" ht="19.5" thickBot="1">
+    <row r="19" spans="2:6" ht="18.600000000000001" thickBot="1">
       <c r="B19" s="28">
         <v>311240</v>
       </c>
@@ -5140,7 +5149,7 @@
         <v>45371</v>
       </c>
     </row>
-    <row r="20" spans="2:6" ht="19.5" thickBot="1">
+    <row r="20" spans="2:6" ht="18.600000000000001" thickBot="1">
       <c r="B20" s="28">
         <v>351333</v>
       </c>
@@ -5157,7 +5166,7 @@
         <v>45297</v>
       </c>
     </row>
-    <row r="21" spans="2:6" ht="19.5" thickBot="1">
+    <row r="21" spans="2:6" ht="18.600000000000001" thickBot="1">
       <c r="B21" s="28">
         <v>671412</v>
       </c>
@@ -5172,7 +5181,7 @@
       </c>
       <c r="F21" s="30"/>
     </row>
-    <row r="22" spans="2:6" ht="19.5" thickBot="1">
+    <row r="22" spans="2:6" ht="18.600000000000001" thickBot="1">
       <c r="B22" s="28">
         <v>887132</v>
       </c>
@@ -5189,7 +5198,7 @@
         <v>45362</v>
       </c>
     </row>
-    <row r="23" spans="2:6" ht="19.5" thickBot="1">
+    <row r="23" spans="2:6" ht="18.600000000000001" thickBot="1">
       <c r="B23" s="28">
         <v>976410</v>
       </c>
@@ -5206,7 +5215,7 @@
         <v>44803</v>
       </c>
     </row>
-    <row r="24" spans="2:6" ht="19.5" thickBot="1">
+    <row r="24" spans="2:6" ht="18.600000000000001" thickBot="1">
       <c r="B24" s="28">
         <v>1016840</v>
       </c>
@@ -5223,7 +5232,7 @@
         <v>45243</v>
       </c>
     </row>
-    <row r="25" spans="2:6" ht="19.5" thickBot="1">
+    <row r="25" spans="2:6" ht="18.600000000000001" thickBot="1">
       <c r="B25" s="28">
         <v>1017119</v>
       </c>
@@ -5240,7 +5249,7 @@
         <v>45256</v>
       </c>
     </row>
-    <row r="26" spans="2:6" ht="19.5" thickBot="1">
+    <row r="26" spans="2:6" ht="18.600000000000001" thickBot="1">
       <c r="B26" s="28">
         <v>1046990</v>
       </c>
@@ -5257,7 +5266,7 @@
         <v>44621</v>
       </c>
     </row>
-    <row r="27" spans="2:6" ht="19.5" thickBot="1">
+    <row r="27" spans="2:6" ht="18.600000000000001" thickBot="1">
       <c r="B27" s="28">
         <v>1106405</v>
       </c>
@@ -5274,7 +5283,7 @@
         <v>45375</v>
       </c>
     </row>
-    <row r="28" spans="2:6" ht="19.5" thickBot="1">
+    <row r="28" spans="2:6" ht="18.600000000000001" thickBot="1">
       <c r="B28" s="28">
         <v>1115600</v>
       </c>
@@ -5291,7 +5300,7 @@
         <v>45288</v>
       </c>
     </row>
-    <row r="29" spans="2:6" ht="19.5" thickBot="1">
+    <row r="29" spans="2:6" ht="18.600000000000001" thickBot="1">
       <c r="B29" s="28">
         <v>1170894</v>
       </c>
@@ -5308,7 +5317,7 @@
         <v>44652</v>
       </c>
     </row>
-    <row r="30" spans="2:6" ht="19.5" thickBot="1">
+    <row r="30" spans="2:6" ht="18.600000000000001" thickBot="1">
       <c r="B30" s="28">
         <v>1193442</v>
       </c>
@@ -5325,7 +5334,7 @@
         <v>44948</v>
       </c>
     </row>
-    <row r="31" spans="2:6" ht="19.5" thickBot="1">
+    <row r="31" spans="2:6" ht="18.600000000000001" thickBot="1">
       <c r="B31" s="28">
         <v>1217756</v>
       </c>
@@ -5342,7 +5351,7 @@
         <v>45009</v>
       </c>
     </row>
-    <row r="32" spans="2:6" ht="19.5" thickBot="1">
+    <row r="32" spans="2:6" ht="18.600000000000001" thickBot="1">
       <c r="B32" s="28">
         <v>1234161</v>
       </c>
@@ -5359,7 +5368,7 @@
         <v>45374</v>
       </c>
     </row>
-    <row r="33" spans="2:6" ht="19.5" thickBot="1">
+    <row r="33" spans="2:6" ht="18.600000000000001" thickBot="1">
       <c r="B33" s="28">
         <v>1316990</v>
       </c>
@@ -5376,7 +5385,7 @@
         <v>45290</v>
       </c>
     </row>
-    <row r="34" spans="2:6" ht="19.5" thickBot="1">
+    <row r="34" spans="2:6" ht="18.600000000000001" thickBot="1">
       <c r="B34" s="28">
         <v>1566705</v>
       </c>
@@ -5393,7 +5402,7 @@
         <v>45322</v>
       </c>
     </row>
-    <row r="35" spans="2:6" ht="19.5" thickBot="1">
+    <row r="35" spans="2:6" ht="18.600000000000001" thickBot="1">
       <c r="B35" s="28">
         <v>1804479</v>
       </c>
@@ -5410,7 +5419,7 @@
         <v>44988</v>
       </c>
     </row>
-    <row r="36" spans="2:6" ht="19.5" thickBot="1">
+    <row r="36" spans="2:6" ht="18.600000000000001" thickBot="1">
       <c r="B36" s="28">
         <v>1840675</v>
       </c>
@@ -5427,7 +5436,7 @@
         <v>45301</v>
       </c>
     </row>
-    <row r="37" spans="2:6" ht="19.5" thickBot="1">
+    <row r="37" spans="2:6" ht="18.600000000000001" thickBot="1">
       <c r="B37" s="28">
         <v>1977301</v>
       </c>
@@ -5444,7 +5453,7 @@
         <v>44976</v>
       </c>
     </row>
-    <row r="38" spans="2:6" ht="19.5" thickBot="1">
+    <row r="38" spans="2:6" ht="18.600000000000001" thickBot="1">
       <c r="B38" s="28">
         <v>2004456</v>
       </c>
@@ -5461,7 +5470,7 @@
         <v>45287</v>
       </c>
     </row>
-    <row r="39" spans="2:6" ht="19.5" thickBot="1">
+    <row r="39" spans="2:6" ht="18.600000000000001" thickBot="1">
       <c r="B39" s="28">
         <v>2086041</v>
       </c>
@@ -5478,7 +5487,7 @@
         <v>45306</v>
       </c>
     </row>
-    <row r="40" spans="2:6" ht="19.5" thickBot="1">
+    <row r="40" spans="2:6" ht="18.600000000000001" thickBot="1">
       <c r="B40" s="28">
         <v>2094113</v>
       </c>
@@ -5495,7 +5504,7 @@
         <v>45347</v>
       </c>
     </row>
-    <row r="41" spans="2:6" ht="19.5" thickBot="1">
+    <row r="41" spans="2:6" ht="18.600000000000001" thickBot="1">
       <c r="B41" s="28">
         <v>2226460</v>
       </c>
@@ -5512,7 +5521,7 @@
         <v>45324</v>
       </c>
     </row>
-    <row r="42" spans="2:6" ht="19.5" thickBot="1">
+    <row r="42" spans="2:6" ht="18.600000000000001" thickBot="1">
       <c r="B42" s="28">
         <v>2234108</v>
       </c>
@@ -5529,7 +5538,7 @@
         <v>44971</v>
       </c>
     </row>
-    <row r="43" spans="2:6" ht="19.5" thickBot="1">
+    <row r="43" spans="2:6" ht="18.600000000000001" thickBot="1">
       <c r="B43" s="28">
         <v>2316474</v>
       </c>
@@ -5546,7 +5555,7 @@
         <v>45262</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="19.5" thickBot="1">
+    <row r="44" spans="2:6" ht="18.600000000000001" thickBot="1">
       <c r="B44" s="28">
         <v>2750902</v>
       </c>
@@ -5563,7 +5572,7 @@
         <v>45375</v>
       </c>
     </row>
-    <row r="45" spans="2:6" ht="19.5" thickBot="1">
+    <row r="45" spans="2:6" ht="18.600000000000001" thickBot="1">
       <c r="B45" s="28">
         <v>2761055</v>
       </c>
@@ -5602,7 +5611,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="49" spans="2:7" ht="19.5" thickBot="1">
+    <row r="49" spans="2:7" ht="18.600000000000001" thickBot="1">
       <c r="B49" s="28">
         <v>51432</v>
       </c>
@@ -5619,7 +5628,7 @@
         <v>45284</v>
       </c>
     </row>
-    <row r="50" spans="2:7" ht="19.5" thickBot="1">
+    <row r="50" spans="2:7" ht="18.600000000000001" thickBot="1">
       <c r="B50" s="28">
         <v>97310</v>
       </c>
@@ -5636,7 +5645,7 @@
         <v>44737</v>
       </c>
     </row>
-    <row r="51" spans="2:7" ht="19.5" thickBot="1">
+    <row r="51" spans="2:7" ht="18.600000000000001" thickBot="1">
       <c r="B51" s="28">
         <v>945671</v>
       </c>
@@ -5675,7 +5684,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="55" spans="2:7" ht="19.5" thickBot="1">
+    <row r="55" spans="2:7" ht="18.600000000000001" thickBot="1">
       <c r="B55" s="35">
         <v>1</v>
       </c>
@@ -5693,7 +5702,7 @@
         <v>41310</v>
       </c>
     </row>
-    <row r="56" spans="2:7" ht="19.5" thickBot="1">
+    <row r="56" spans="2:7" ht="18.600000000000001" thickBot="1">
       <c r="B56" s="35">
         <v>2</v>
       </c>
@@ -5711,7 +5720,7 @@
       </c>
       <c r="G56" s="30"/>
     </row>
-    <row r="57" spans="2:7" ht="19.5" thickBot="1">
+    <row r="57" spans="2:7" ht="18.600000000000001" thickBot="1">
       <c r="B57" s="35">
         <v>3</v>
       </c>
@@ -5729,7 +5738,7 @@
         <v>19000</v>
       </c>
     </row>
-    <row r="58" spans="2:7" ht="19.5" thickBot="1">
+    <row r="58" spans="2:7" ht="18.600000000000001" thickBot="1">
       <c r="B58" s="35">
         <v>4</v>
       </c>
@@ -5745,7 +5754,7 @@
       <c r="F58" s="30"/>
       <c r="G58" s="30"/>
     </row>
-    <row r="59" spans="2:7" ht="19.5" thickBot="1">
+    <row r="59" spans="2:7" ht="18.600000000000001" thickBot="1">
       <c r="B59" s="35">
         <v>5</v>
       </c>
@@ -5763,7 +5772,7 @@
       </c>
       <c r="G59" s="30"/>
     </row>
-    <row r="60" spans="2:7" ht="19.5" thickBot="1">
+    <row r="60" spans="2:7" ht="18.600000000000001" thickBot="1">
       <c r="B60" s="35">
         <v>6</v>
       </c>
@@ -5781,7 +5790,7 @@
       </c>
       <c r="G60" s="30"/>
     </row>
-    <row r="61" spans="2:7" ht="19.5" thickBot="1">
+    <row r="61" spans="2:7" ht="18.600000000000001" thickBot="1">
       <c r="B61" s="35">
         <v>7</v>
       </c>
@@ -5799,7 +5808,7 @@
       </c>
       <c r="G61" s="30"/>
     </row>
-    <row r="62" spans="2:7" ht="19.5" thickBot="1">
+    <row r="62" spans="2:7" ht="18.600000000000001" thickBot="1">
       <c r="B62" s="35">
         <v>8</v>
       </c>
@@ -5817,7 +5826,7 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="63" spans="2:7" ht="19.5" thickBot="1">
+    <row r="63" spans="2:7" ht="18.600000000000001" thickBot="1">
       <c r="B63" s="35">
         <v>9</v>
       </c>
@@ -5835,7 +5844,7 @@
       </c>
       <c r="G63" s="30"/>
     </row>
-    <row r="64" spans="2:7" ht="19.5" thickBot="1">
+    <row r="64" spans="2:7" ht="18.600000000000001" thickBot="1">
       <c r="B64" s="35">
         <v>10</v>
       </c>
@@ -5853,7 +5862,7 @@
       </c>
       <c r="G64" s="30"/>
     </row>
-    <row r="65" spans="2:7" ht="19.5" thickBot="1">
+    <row r="65" spans="2:7" ht="18.600000000000001" thickBot="1">
       <c r="B65" s="35">
         <v>11</v>
       </c>
@@ -5871,7 +5880,7 @@
       </c>
       <c r="G65" s="30"/>
     </row>
-    <row r="66" spans="2:7" ht="19.5" thickBot="1">
+    <row r="66" spans="2:7" ht="18.600000000000001" thickBot="1">
       <c r="B66" s="35">
         <v>12</v>
       </c>
@@ -5889,7 +5898,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="67" spans="2:7" ht="19.5" thickBot="1">
+    <row r="67" spans="2:7" ht="18.600000000000001" thickBot="1">
       <c r="B67" s="35">
         <v>13</v>
       </c>
@@ -5907,7 +5916,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="68" spans="2:7" ht="19.5" thickBot="1">
+    <row r="68" spans="2:7" ht="18.600000000000001" thickBot="1">
       <c r="B68" s="35">
         <v>14</v>
       </c>
@@ -5925,7 +5934,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="69" spans="2:7" ht="19.5" thickBot="1">
+    <row r="69" spans="2:7" ht="18.600000000000001" thickBot="1">
       <c r="B69" s="35">
         <v>15</v>
       </c>
@@ -5943,7 +5952,7 @@
       </c>
       <c r="G69" s="30"/>
     </row>
-    <row r="70" spans="2:7" ht="19.5" thickBot="1">
+    <row r="70" spans="2:7" ht="18.600000000000001" thickBot="1">
       <c r="B70" s="35">
         <v>16</v>
       </c>
@@ -5961,7 +5970,7 @@
       </c>
       <c r="G70" s="30"/>
     </row>
-    <row r="71" spans="2:7" ht="19.5" thickBot="1">
+    <row r="71" spans="2:7" ht="18.600000000000001" thickBot="1">
       <c r="B71" s="35">
         <v>17</v>
       </c>
@@ -5979,7 +5988,7 @@
       </c>
       <c r="G71" s="30"/>
     </row>
-    <row r="72" spans="2:7" ht="19.5" thickBot="1">
+    <row r="72" spans="2:7" ht="18.600000000000001" thickBot="1">
       <c r="B72" s="35">
         <v>18</v>
       </c>
@@ -5997,7 +6006,7 @@
         <v>12600</v>
       </c>
     </row>
-    <row r="73" spans="2:7" ht="19.5" thickBot="1">
+    <row r="73" spans="2:7" ht="18.600000000000001" thickBot="1">
       <c r="B73" s="35">
         <v>19</v>
       </c>
@@ -6015,7 +6024,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="74" spans="2:7" ht="19.5" thickBot="1">
+    <row r="74" spans="2:7" ht="18.600000000000001" thickBot="1">
       <c r="B74" s="35">
         <v>20</v>
       </c>
@@ -6033,7 +6042,7 @@
       </c>
       <c r="G74" s="30"/>
     </row>
-    <row r="75" spans="2:7" ht="19.5" thickBot="1">
+    <row r="75" spans="2:7" ht="18.600000000000001" thickBot="1">
       <c r="B75" s="35">
         <v>21</v>
       </c>
@@ -6051,7 +6060,7 @@
       </c>
       <c r="G75" s="30"/>
     </row>
-    <row r="76" spans="2:7" ht="19.5" thickBot="1">
+    <row r="76" spans="2:7" ht="18.600000000000001" thickBot="1">
       <c r="B76" s="35">
         <v>22</v>
       </c>
@@ -6069,7 +6078,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="77" spans="2:7" ht="19.5" thickBot="1">
+    <row r="77" spans="2:7" ht="18.600000000000001" thickBot="1">
       <c r="B77" s="35">
         <v>23</v>
       </c>
@@ -6085,7 +6094,7 @@
       <c r="F77" s="30"/>
       <c r="G77" s="30"/>
     </row>
-    <row r="78" spans="2:7" ht="19.5" thickBot="1">
+    <row r="78" spans="2:7" ht="18.600000000000001" thickBot="1">
       <c r="B78" s="35">
         <v>24</v>
       </c>
@@ -6103,7 +6112,7 @@
       </c>
       <c r="G78" s="30"/>
     </row>
-    <row r="79" spans="2:7" ht="19.5" thickBot="1">
+    <row r="79" spans="2:7" ht="18.600000000000001" thickBot="1">
       <c r="B79" s="35">
         <v>25</v>
       </c>
@@ -6121,7 +6130,7 @@
         <v>55000</v>
       </c>
     </row>
-    <row r="80" spans="2:7" ht="19.5" thickBot="1">
+    <row r="80" spans="2:7" ht="18.600000000000001" thickBot="1">
       <c r="B80" s="35">
         <v>26</v>
       </c>
@@ -6139,7 +6148,7 @@
         <v>15100</v>
       </c>
     </row>
-    <row r="81" spans="2:7" ht="19.5" thickBot="1">
+    <row r="81" spans="2:7" ht="18.600000000000001" thickBot="1">
       <c r="B81" s="35">
         <v>27</v>
       </c>
@@ -6157,7 +6166,7 @@
         <v>36591</v>
       </c>
     </row>
-    <row r="82" spans="2:7" ht="19.5" thickBot="1">
+    <row r="82" spans="2:7" ht="18.600000000000001" thickBot="1">
       <c r="B82" s="35">
         <v>28</v>
       </c>
@@ -6193,7 +6202,7 @@
       </c>
       <c r="G83" s="33"/>
     </row>
-    <row r="86" spans="2:7" ht="19.5" thickBot="1">
+    <row r="86" spans="2:7" ht="18.600000000000001" thickBot="1">
       <c r="B86" s="36">
         <v>1</v>
       </c>
@@ -6201,7 +6210,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="87" spans="2:7" ht="19.5" thickBot="1">
+    <row r="87" spans="2:7" ht="18.600000000000001" thickBot="1">
       <c r="B87" s="36">
         <v>2</v>
       </c>
@@ -6209,7 +6218,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="88" spans="2:7" ht="19.5" thickBot="1">
+    <row r="88" spans="2:7" ht="18.600000000000001" thickBot="1">
       <c r="B88" s="36">
         <v>3</v>
       </c>
@@ -6217,7 +6226,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="89" spans="2:7" ht="19.5" thickBot="1">
+    <row r="89" spans="2:7" ht="18.600000000000001" thickBot="1">
       <c r="B89" s="36">
         <v>4</v>
       </c>
@@ -6225,7 +6234,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="90" spans="2:7" ht="19.5" thickBot="1">
+    <row r="90" spans="2:7" ht="18.600000000000001" thickBot="1">
       <c r="B90" s="36">
         <v>5</v>
       </c>
@@ -6233,7 +6242,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="91" spans="2:7" ht="19.5" thickBot="1">
+    <row r="91" spans="2:7" ht="18.600000000000001" thickBot="1">
       <c r="B91" s="36">
         <v>6</v>
       </c>
@@ -6260,9 +6269,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C74CC05-0B9A-4E01-BB17-84F783EA8B46}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="B2:I56"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="4.625" customWidth="1"/>
+    <col min="1" max="1" width="4.59765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:9">
